--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-historique-des-grossesses.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-historique-des-grossesses.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:52:47+00:00</t>
+    <t>2026-04-16T09:27:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-historique-des-grossesses.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-historique-des-grossesses.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:27:41+00:00</t>
+    <t>2026-04-16T09:55:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-historique-des-grossesses.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-historique-des-grossesses.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:55:40+00:00</t>
+    <t>2026-04-16T10:39:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-historique-des-grossesses.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-historique-des-grossesses.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3205" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3207" uniqueCount="335">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T10:39:58+00:00</t>
+    <t>2026-04-17T08:40:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -505,10 +505,13 @@
     <t>Section.id</t>
   </si>
   <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Identifiant de la section</t>
+  </si>
+  <si>
     <t>Section.code</t>
-  </si>
-  <si>
-    <t>Y</t>
   </si>
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CE
@@ -4070,7 +4073,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>158</v>
       </c>
@@ -4089,7 +4092,7 @@
         <v>75</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>74</v>
+        <v>159</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>74</v>
@@ -4100,8 +4103,12 @@
       <c r="K27" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="L27" s="2"/>
-      <c r="M27" s="2"/>
+      <c r="L27" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4171,10 +4178,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4188,7 +4195,7 @@
         <v>75</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>74</v>
@@ -4197,13 +4204,13 @@
         <v>74</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4254,7 +4261,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -4274,10 +4281,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4373,12 +4380,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4388,13 +4395,13 @@
         <v>62</v>
       </c>
       <c r="F30" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>74</v>
+        <v>159</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>74</v>
@@ -4407,7 +4414,7 @@
       </c>
       <c r="L30" s="2"/>
       <c r="M30" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4419,7 +4426,7 @@
         <v>74</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T30" t="s" s="2">
         <v>74</v>
@@ -4458,7 +4465,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -4476,28 +4483,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>74</v>
+        <v>159</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>74</v>
@@ -4510,7 +4517,7 @@
       </c>
       <c r="L31" s="2"/>
       <c r="M31" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4522,7 +4529,7 @@
         <v>74</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="T31" t="s" s="2">
         <v>74</v>
@@ -4561,7 +4568,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -4581,17 +4588,17 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F32" t="s" s="2">
         <v>80</v>
@@ -4613,7 +4620,7 @@
       </c>
       <c r="L32" s="2"/>
       <c r="M32" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4625,7 +4632,7 @@
         <v>74</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="T32" t="s" s="2">
         <v>74</v>
@@ -4664,7 +4671,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -4684,17 +4691,17 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>80</v>
@@ -4716,7 +4723,7 @@
       </c>
       <c r="L33" s="2"/>
       <c r="M33" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4767,7 +4774,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -4785,28 +4792,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E34" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F34" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>74</v>
+        <v>159</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>74</v>
@@ -4819,7 +4826,7 @@
       </c>
       <c r="L34" s="2"/>
       <c r="M34" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4831,7 +4838,7 @@
         <v>74</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>74</v>
@@ -4870,7 +4877,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -4890,10 +4897,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4916,11 +4923,11 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L35" s="2"/>
       <c r="M35" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4971,7 +4978,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -4991,10 +4998,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5021,7 +5028,7 @@
       </c>
       <c r="L36" s="2"/>
       <c r="M36" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5072,7 +5079,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -5092,17 +5099,17 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>80</v>
@@ -5120,11 +5127,11 @@
         <v>74</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5175,7 +5182,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5195,17 +5202,17 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>80</v>
@@ -5223,11 +5230,11 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L38" s="2"/>
       <c r="M38" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5278,7 +5285,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -5298,17 +5305,17 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>80</v>
@@ -5326,11 +5333,11 @@
         <v>74</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5381,7 +5388,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -5401,10 +5408,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5418,7 +5425,7 @@
         <v>75</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>74</v>
@@ -5427,13 +5434,13 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5484,7 +5491,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5504,10 +5511,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5521,7 +5528,7 @@
         <v>75</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>74</v>
@@ -5530,13 +5537,13 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5587,7 +5594,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -5607,10 +5614,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5633,7 +5640,7 @@
         <v>74</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L42" s="2"/>
       <c r="M42" s="2"/>
@@ -5686,7 +5693,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5706,10 +5713,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5765,25 +5772,25 @@
       </c>
       <c r="Y43" s="2"/>
       <c r="Z43" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF43" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -5803,10 +5810,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5829,7 +5836,7 @@
         <v>74</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" s="2"/>
@@ -5882,7 +5889,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -5902,10 +5909,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5928,7 +5935,7 @@
         <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
@@ -5981,7 +5988,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -6001,10 +6008,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6027,7 +6034,7 @@
         <v>74</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L46" s="2"/>
       <c r="M46" s="2"/>
@@ -6080,7 +6087,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -6100,10 +6107,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6117,7 +6124,7 @@
         <v>81</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>74</v>
@@ -6126,7 +6133,7 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L47" s="2"/>
       <c r="M47" s="2"/>
@@ -6167,7 +6174,7 @@
         <v>74</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AC47" s="2"/>
       <c r="AD47" t="s" s="2">
@@ -6177,7 +6184,7 @@
         <v>124</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -6197,13 +6204,13 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>74</v>
@@ -6225,7 +6232,7 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
@@ -6278,7 +6285,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -6298,10 +6305,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6399,10 +6406,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6500,10 +6507,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6601,10 +6608,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6702,10 +6709,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6805,10 +6812,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6908,10 +6915,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7011,10 +7018,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7114,10 +7121,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7215,10 +7222,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7248,7 +7255,7 @@
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q58" s="2"/>
       <c r="R58" t="s" s="2">
@@ -7274,7 +7281,7 @@
       </c>
       <c r="Y58" s="2"/>
       <c r="Z58" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>74</v>
@@ -7292,7 +7299,7 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -7312,10 +7319,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7349,7 +7356,7 @@
       </c>
       <c r="Q59" s="2"/>
       <c r="R59" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="S59" t="s" s="2">
         <v>74</v>
@@ -7391,7 +7398,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -7411,10 +7418,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7437,7 +7444,7 @@
         <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
@@ -7490,7 +7497,7 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -7510,10 +7517,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7536,7 +7543,7 @@
         <v>74</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L61" s="2"/>
       <c r="M61" s="2"/>
@@ -7589,7 +7596,7 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -7609,10 +7616,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7635,10 +7642,10 @@
         <v>74</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M62" s="2"/>
       <c r="N62" s="2"/>
@@ -7690,7 +7697,7 @@
         <v>74</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -7710,10 +7717,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7736,7 +7743,7 @@
         <v>74</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L63" s="2"/>
       <c r="M63" s="2"/>
@@ -7789,7 +7796,7 @@
         <v>74</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -7809,10 +7816,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7835,7 +7842,7 @@
         <v>74</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L64" s="2"/>
       <c r="M64" s="2"/>
@@ -7888,7 +7895,7 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -7908,10 +7915,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -7934,7 +7941,7 @@
         <v>74</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L65" s="2"/>
       <c r="M65" s="2"/>
@@ -7987,7 +7994,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -8007,10 +8014,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8033,7 +8040,7 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
@@ -8086,7 +8093,7 @@
         <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -8106,10 +8113,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8132,7 +8139,7 @@
         <v>74</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L67" s="2"/>
       <c r="M67" s="2"/>
@@ -8185,7 +8192,7 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -8205,10 +8212,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8231,7 +8238,7 @@
         <v>74</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L68" s="2"/>
       <c r="M68" s="2"/>
@@ -8284,7 +8291,7 @@
         <v>74</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -8304,13 +8311,13 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D69" t="s" s="2">
         <v>74</v>
@@ -8332,7 +8339,7 @@
         <v>74</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L69" s="2"/>
       <c r="M69" s="2"/>
@@ -8385,7 +8392,7 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -8405,10 +8412,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8506,10 +8513,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8607,10 +8614,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8708,10 +8715,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8809,10 +8816,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -8912,10 +8919,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9015,10 +9022,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9118,10 +9125,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9221,10 +9228,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9322,10 +9329,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9355,7 +9362,7 @@
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q79" s="2"/>
       <c r="R79" t="s" s="2">
@@ -9381,7 +9388,7 @@
       </c>
       <c r="Y79" s="2"/>
       <c r="Z79" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>74</v>
@@ -9399,7 +9406,7 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -9419,10 +9426,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9456,7 +9463,7 @@
       </c>
       <c r="Q80" s="2"/>
       <c r="R80" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="S80" t="s" s="2">
         <v>74</v>
@@ -9498,7 +9505,7 @@
         <v>74</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -9518,10 +9525,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9544,7 +9551,7 @@
         <v>74</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L81" s="2"/>
       <c r="M81" s="2"/>
@@ -9597,7 +9604,7 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -9617,10 +9624,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9643,7 +9650,7 @@
         <v>74</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L82" s="2"/>
       <c r="M82" s="2"/>
@@ -9696,7 +9703,7 @@
         <v>74</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -9716,10 +9723,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9742,7 +9749,7 @@
         <v>74</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L83" s="2"/>
       <c r="M83" s="2"/>
@@ -9795,7 +9802,7 @@
         <v>74</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -9815,10 +9822,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -9841,7 +9848,7 @@
         <v>74</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L84" s="2"/>
       <c r="M84" s="2"/>
@@ -9894,7 +9901,7 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -9914,10 +9921,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -9940,10 +9947,10 @@
         <v>74</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M85" s="2"/>
       <c r="N85" s="2"/>
@@ -9995,7 +10002,7 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -10015,10 +10022,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10041,7 +10048,7 @@
         <v>74</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
@@ -10094,7 +10101,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -10114,10 +10121,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10140,7 +10147,7 @@
         <v>74</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L87" s="2"/>
       <c r="M87" s="2"/>
@@ -10193,7 +10200,7 @@
         <v>74</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -10213,10 +10220,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10239,7 +10246,7 @@
         <v>74</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L88" s="2"/>
       <c r="M88" s="2"/>
@@ -10292,7 +10299,7 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -10312,10 +10319,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10338,7 +10345,7 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L89" s="2"/>
       <c r="M89" s="2"/>
@@ -10391,7 +10398,7 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -10411,10 +10418,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10437,7 +10444,7 @@
         <v>74</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L90" s="2"/>
       <c r="M90" s="2"/>
@@ -10490,7 +10497,7 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -10510,10 +10517,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10611,10 +10618,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10712,10 +10719,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -10813,10 +10820,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -10914,10 +10921,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11017,10 +11024,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11120,10 +11127,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11223,10 +11230,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11326,10 +11333,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11427,10 +11434,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11457,7 +11464,7 @@
       </c>
       <c r="L100" s="2"/>
       <c r="M100" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -11466,7 +11473,7 @@
       </c>
       <c r="Q100" s="2"/>
       <c r="R100" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="S100" t="s" s="2">
         <v>74</v>
@@ -11508,7 +11515,7 @@
         <v>74</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -11528,10 +11535,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -11565,7 +11572,7 @@
       </c>
       <c r="Q101" s="2"/>
       <c r="R101" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="S101" t="s" s="2">
         <v>74</v>
@@ -11607,7 +11614,7 @@
         <v>74</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -11627,10 +11634,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -11653,7 +11660,7 @@
         <v>74</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L102" s="2"/>
       <c r="M102" s="2"/>
@@ -11706,7 +11713,7 @@
         <v>74</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>75</v>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-historique-des-grossesses.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-historique-des-grossesses.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T08:40:59+00:00</t>
+    <t>2026-04-17T11:35:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-historique-des-grossesses.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-historique-des-grossesses.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T11:35:08+00:00</t>
+    <t>2026-04-20T14:26:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
